--- a/TP4/resultados_logit_2025.xlsx
+++ b/TP4/resultados_logit_2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,54 +462,415 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.676604337391814</v>
+        <v>-5.53065448639288</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2282945819621358</v>
+        <v>1.49736726240327</v>
       </c>
       <c r="D2" t="n">
-        <v>2.072425304448224e-13</v>
+        <v>0.0002211138403966281</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1870079148930793</v>
+        <v>0.003963394252433213</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>edad</t>
+          <t>Distincion_vivienda_hogar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.01654030553028782</v>
+        <v>-0.1203869569307996</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003176426480500398</v>
+        <v>0.4528034689423282</v>
       </c>
       <c r="D3" t="n">
-        <v>1.917057201592816e-07</v>
+        <v>0.7903391625331845</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9835957342440609</v>
+        <v>0.8865773031003492</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>genero</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.4514219826275524</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.2391499254893375</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.05907821887533246</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.570543884515089</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>edad</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.07459481019366809</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.03275324859065769</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.02275768398669165</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.077447491685189</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tipo_empleo</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.09954120572331254</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.06375827430209352</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1184699549204195</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.104663988280809</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>parentesco</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.09499107434378663</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.03127978336373496</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.002390881147907906</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.099649039993013</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>nivel_educ</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.00100297202588646</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.05365638347191233</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.9850864101867165</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9989975307824409</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>estado_empleo</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.004672006983337665</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.2247301276506222</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.98341364472878</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.004682937824323</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>categoria_inactividad</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.3221084103009738</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.08380863710863888</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0001213515221442432</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.38003437779016</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tipo_cobertura_salud</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.6087947924575512</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.2573000540901003</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.01797712887409524</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.5440061144141038</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>obra_social</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.5271829834189674</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.1658489537723312</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.00147940460259617</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.5902654172937982</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>nivel_ocupacion</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.2445091347071878</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1165353117227254</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.03589146461429586</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.7830888350454829</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tipo_contrato</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.4143899663525604</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.05354728625362221</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.00385633952258e-14</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.513447205307998</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>empleo</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.1157082061627584</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.2277547391159025</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.6114262507430259</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.122668236661849</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>busqueda_empleo</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.335880039946003</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.3303500931691885</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5.258476704814857e-05</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.803341566570534</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>medio_busqueda_empleo</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-11.61913132423539</v>
+      </c>
+      <c r="C17" t="n">
+        <v>13313.00404310262</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.999303633929158</v>
+      </c>
+      <c r="E17" t="n">
+        <v>8.99239512235424e-06</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>n_personas</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.3763611060843097</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.1885402361338874</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.04591383872356278</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.456973160662606</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adulto_equiv</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3.762711438993961</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.087055163998389</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.0005374128489220079</v>
+      </c>
+      <c r="E19" t="n">
+        <v>43.06503603477545</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>ad_equiv_hogar</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>0.2476887473182485</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.05417463595413832</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4.829925444921813e-06</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1.281061136419915</v>
+      <c r="B20" t="n">
+        <v>-0.2803599571191871</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.22780238560925</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.2184292392343662</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7555117406746683</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>edad2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-0.000989782596305582</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.0003657686485565396</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.00680919635142492</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9990107070769184</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>educ</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>-0.0518864288170729</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.05119741323271384</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.3108414402860883</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9494366893679337</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>horastrab</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-0.01869983132407619</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.003744666554752594</v>
+      </c>
+      <c r="D23" t="n">
+        <v>5.922601407649122e-07</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9814739257599729</v>
       </c>
     </row>
   </sheetData>
